--- a/reviews/ITINERARY-2026-07-14-apollo-component-library.xlsx
+++ b/reviews/ITINERARY-2026-07-14-apollo-component-library.xlsx
@@ -825,17 +825,17 @@
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>Gap</t>
+          <t>Gated</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1 Foundations</t>
+          <t>0 Have</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>Reliability-critical; used everywhere.</t>
+          <t>Reviewed + gated 2026-07-20 — Mono button/* ladder, real sprite glyphs, icon-015 4.5:1</t>
         </is>
       </c>
     </row>
